--- a/output/topology_excel/2086.xlsx
+++ b/output/topology_excel/2086.xlsx
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B23" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B24" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B25" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B27" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B29" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B30" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="B31" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="B32" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="B33" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="B35" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B36" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B37" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B38" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B39" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B40" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B42" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="B43" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="B45" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="B47" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="B48" t="n">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="B49" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="B50" t="n">
         <v>55</v>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n">
         <v>55</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="B52" t="n">
         <v>56</v>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B53" t="n">
         <v>55</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B54" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B55" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B56" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B57" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F58" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59">
@@ -1719,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="B59" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>707</v>
+        <v>510</v>
       </c>
       <c r="F59" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60">
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="B60" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1752,18 +1752,18 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>87</v>
+        <v>297</v>
       </c>
       <c r="F60" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1774,18 +1774,18 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F61" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B62" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1796,10 +1796,10 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>229</v>
+        <v>385</v>
       </c>
       <c r="F62" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
@@ -1807,7 +1807,7 @@
         <v>2</v>
       </c>
       <c r="B63" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>29</v>
+        <v>469</v>
       </c>
       <c r="F63" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
@@ -1829,7 +1829,7 @@
         <v>2</v>
       </c>
       <c r="B64" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>194</v>
+        <v>124</v>
       </c>
       <c r="F64" t="n">
-        <v>109</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
@@ -1851,7 +1851,7 @@
         <v>2</v>
       </c>
       <c r="B65" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1862,10 +1862,10 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>78</v>
+        <v>325</v>
       </c>
       <c r="F65" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66">
@@ -1873,7 +1873,7 @@
         <v>2</v>
       </c>
       <c r="B66" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1884,10 +1884,10 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>85</v>
+        <v>168</v>
       </c>
       <c r="F66" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
@@ -1895,7 +1895,7 @@
         <v>2</v>
       </c>
       <c r="B67" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1906,10 +1906,10 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>113</v>
+        <v>524</v>
       </c>
       <c r="F67" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
@@ -1917,7 +1917,7 @@
         <v>2</v>
       </c>
       <c r="B68" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1928,10 +1928,10 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>107</v>
+        <v>297</v>
       </c>
       <c r="F68" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69">
@@ -1939,7 +1939,7 @@
         <v>2</v>
       </c>
       <c r="B69" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1950,18 +1950,18 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F69" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B70" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1972,10 +1972,10 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>54</v>
+        <v>510</v>
       </c>
       <c r="F70" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71">
@@ -1994,18 +1994,18 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>103</v>
+        <v>347</v>
       </c>
       <c r="F71" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B72" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2016,18 +2016,18 @@
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>132</v>
+        <v>524</v>
       </c>
       <c r="F72" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B73" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>651</v>
+        <v>194</v>
       </c>
       <c r="F73" t="n">
-        <v>17</v>
+        <v>109</v>
       </c>
     </row>
     <row r="74">
@@ -2049,7 +2049,7 @@
         <v>5</v>
       </c>
       <c r="B74" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="F74" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
@@ -2071,7 +2071,7 @@
         <v>5</v>
       </c>
       <c r="B75" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2082,18 +2082,18 @@
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="F75" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B76" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -2104,18 +2104,18 @@
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="F76" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B77" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -2126,18 +2126,18 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>682</v>
+        <v>146</v>
       </c>
       <c r="F77" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B78" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>88</v>
+        <v>269</v>
       </c>
       <c r="F78" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79">
@@ -2159,7 +2159,7 @@
         <v>7</v>
       </c>
       <c r="B79" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2170,10 +2170,10 @@
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>182</v>
+        <v>269</v>
       </c>
       <c r="F79" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
@@ -2181,7 +2181,7 @@
         <v>7</v>
       </c>
       <c r="B80" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -2192,18 +2192,18 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="F80" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B81" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -2214,18 +2214,18 @@
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>97</v>
+        <v>237</v>
       </c>
       <c r="F81" t="n">
-        <v>19</v>
+        <v>164</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B82" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -2236,18 +2236,18 @@
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>798</v>
+        <v>211</v>
       </c>
       <c r="F82" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B83" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -2258,10 +2258,10 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F83" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84">
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
       <c r="B84" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="F84" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85">
@@ -2291,7 +2291,7 @@
         <v>9</v>
       </c>
       <c r="B85" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -2302,10 +2302,10 @@
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="F85" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86">
@@ -2313,7 +2313,7 @@
         <v>10</v>
       </c>
       <c r="B86" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="F86" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87">
@@ -2335,7 +2335,7 @@
         <v>10</v>
       </c>
       <c r="B87" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2346,18 +2346,18 @@
         <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="F87" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B88" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2368,10 +2368,10 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="F88" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89">
@@ -2379,7 +2379,7 @@
         <v>11</v>
       </c>
       <c r="B89" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2390,18 +2390,18 @@
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="F89" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B90" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2412,18 +2412,18 @@
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="F90" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B91" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2434,18 +2434,18 @@
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>107</v>
+        <v>634</v>
       </c>
       <c r="F91" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B92" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2456,18 +2456,18 @@
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="F92" t="n">
-        <v>12</v>
+        <v>181</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B93" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2478,18 +2478,18 @@
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="F93" t="n">
-        <v>12</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B94" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2500,40 +2500,40 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>163</v>
+        <v>297</v>
       </c>
       <c r="F94" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B95" t="n">
+        <v>45</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>146</v>
+      </c>
+      <c r="F95" t="n">
         <v>16</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" t="n">
-        <v>651</v>
-      </c>
-      <c r="F95" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B96" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -2544,18 +2544,18 @@
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>408</v>
+        <v>146</v>
       </c>
       <c r="F96" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B97" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -2566,18 +2566,18 @@
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>124</v>
+        <v>304</v>
       </c>
       <c r="F97" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B98" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2588,18 +2588,18 @@
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>408</v>
+        <v>304</v>
       </c>
       <c r="F98" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B99" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2610,62 +2610,62 @@
         <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>108</v>
+        <v>181</v>
       </c>
       <c r="F99" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
+        <v>14</v>
+      </c>
+      <c r="B100" t="n">
+        <v>51</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>73</v>
+      </c>
+      <c r="F100" t="n">
         <v>17</v>
-      </c>
-      <c r="B100" t="n">
-        <v>19</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" t="n">
-        <v>572</v>
-      </c>
-      <c r="F100" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
+        <v>14</v>
+      </c>
+      <c r="B101" t="n">
+        <v>44</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>121</v>
+      </c>
+      <c r="F101" t="n">
         <v>17</v>
-      </c>
-      <c r="B101" t="n">
-        <v>20</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" t="n">
-        <v>120</v>
-      </c>
-      <c r="F101" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B102" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2676,18 +2676,18 @@
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="F102" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B103" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -2698,18 +2698,18 @@
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>625</v>
+        <v>87</v>
       </c>
       <c r="F103" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B104" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2720,19 +2720,19 @@
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>124</v>
+        <v>229</v>
       </c>
       <c r="F104" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
+        <v>15</v>
+      </c>
+      <c r="B105" t="n">
         <v>21</v>
       </c>
-      <c r="B105" t="n">
-        <v>22</v>
-      </c>
       <c r="C105" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -2742,18 +2742,18 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>108</v>
+        <v>229</v>
       </c>
       <c r="F105" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B106" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -2764,18 +2764,18 @@
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="F106" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B107" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2786,18 +2786,18 @@
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>297</v>
+        <v>75</v>
       </c>
       <c r="F107" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B108" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2808,18 +2808,18 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F108" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B109" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -2830,18 +2830,18 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F109" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B110" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2852,40 +2852,40 @@
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>304</v>
+        <v>181</v>
       </c>
       <c r="F110" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B111" t="n">
+        <v>21</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="n">
         <v>54</v>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" t="n">
-        <v>110</v>
-      </c>
       <c r="F111" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B112" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2896,18 +2896,18 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="F112" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B113" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2918,18 +2918,18 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="F113" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B114" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2940,18 +2940,18 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>510</v>
+        <v>163</v>
       </c>
       <c r="F114" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B115" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -2962,18 +2962,18 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>297</v>
+        <v>165</v>
       </c>
       <c r="F115" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B116" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2984,18 +2984,18 @@
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="F116" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B117" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -3006,18 +3006,18 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>385</v>
+        <v>255</v>
       </c>
       <c r="F117" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B118" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -3028,18 +3028,18 @@
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>510</v>
+        <v>69</v>
       </c>
       <c r="F118" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B119" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -3050,18 +3050,18 @@
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>401</v>
+        <v>98</v>
       </c>
       <c r="F119" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B120" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -3072,18 +3072,18 @@
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>469</v>
+        <v>707</v>
       </c>
       <c r="F120" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B121" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -3094,40 +3094,40 @@
         <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>347</v>
+        <v>103</v>
       </c>
       <c r="F121" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B122" t="n">
+        <v>25</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="n">
         <v>29</v>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" t="n">
-        <v>124</v>
-      </c>
       <c r="F122" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B123" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -3138,18 +3138,18 @@
         <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>325</v>
+        <v>85</v>
       </c>
       <c r="F123" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B124" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -3160,19 +3160,19 @@
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>168</v>
+        <v>113</v>
       </c>
       <c r="F124" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
+        <v>21</v>
+      </c>
+      <c r="B125" t="n">
         <v>28</v>
       </c>
-      <c r="B125" t="n">
-        <v>43</v>
-      </c>
       <c r="C125" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -3182,18 +3182,18 @@
         <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>524</v>
+        <v>107</v>
       </c>
       <c r="F125" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B126" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -3204,18 +3204,18 @@
         <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>297</v>
+        <v>84</v>
       </c>
       <c r="F126" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B127" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -3226,18 +3226,18 @@
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="F127" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B128" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -3248,18 +3248,18 @@
         <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F128" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B129" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -3270,19 +3270,19 @@
         <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>165</v>
+        <v>651</v>
       </c>
       <c r="F129" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
+        <v>24</v>
+      </c>
+      <c r="B130" t="n">
         <v>30</v>
       </c>
-      <c r="B130" t="n">
-        <v>32</v>
-      </c>
       <c r="C130" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -3292,18 +3292,18 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>325</v>
+        <v>79</v>
       </c>
       <c r="F130" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B131" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -3314,18 +3314,18 @@
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>634</v>
+        <v>682</v>
       </c>
       <c r="F131" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B132" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -3336,18 +3336,18 @@
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>184</v>
+        <v>97</v>
       </c>
       <c r="F132" t="n">
-        <v>181</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B133" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -3358,18 +3358,18 @@
         <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>180</v>
+        <v>798</v>
       </c>
       <c r="F133" t="n">
-        <v>98</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B134" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -3380,18 +3380,18 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="F134" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B135" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -3402,18 +3402,18 @@
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="F135" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B136" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -3424,18 +3424,18 @@
         <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>237</v>
+        <v>75</v>
       </c>
       <c r="F136" t="n">
-        <v>164</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B137" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -3446,18 +3446,18 @@
         <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>252</v>
+        <v>113</v>
       </c>
       <c r="F137" t="n">
-        <v>226</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B138" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -3468,18 +3468,18 @@
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>332</v>
+        <v>75</v>
       </c>
       <c r="F138" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B139" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -3490,18 +3490,18 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>208</v>
+        <v>107</v>
       </c>
       <c r="F139" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B140" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -3512,18 +3512,18 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>269</v>
+        <v>84</v>
       </c>
       <c r="F140" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B141" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -3534,18 +3534,18 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>77</v>
+        <v>651</v>
       </c>
       <c r="F141" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B142" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -3556,18 +3556,18 @@
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>255</v>
+        <v>408</v>
       </c>
       <c r="F142" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B143" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -3578,18 +3578,18 @@
         <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>269</v>
+        <v>124</v>
       </c>
       <c r="F143" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B144" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -3600,18 +3600,18 @@
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>99</v>
+        <v>408</v>
       </c>
       <c r="F144" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B145" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -3622,18 +3622,18 @@
         <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="F145" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B146" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -3644,18 +3644,18 @@
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>121</v>
+        <v>572</v>
       </c>
       <c r="F146" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B147" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -3666,18 +3666,18 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="F147" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B148" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -3688,18 +3688,18 @@
         <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F148" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B149" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -3710,18 +3710,18 @@
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>78</v>
+        <v>625</v>
       </c>
       <c r="F149" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B150" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -3732,18 +3732,18 @@
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="F150" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B151" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -3754,18 +3754,18 @@
         <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>524</v>
+        <v>108</v>
       </c>
       <c r="F151" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B152" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -3776,18 +3776,18 @@
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>304</v>
+        <v>80</v>
       </c>
       <c r="F152" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B153" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -3798,18 +3798,18 @@
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="F153" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B154" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -3820,18 +3820,18 @@
         <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>524</v>
+        <v>401</v>
       </c>
       <c r="F154" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B155" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -3842,18 +3842,18 @@
         <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="F155" t="n">
-        <v>13</v>
+        <v>226</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B156" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -3864,18 +3864,18 @@
         <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>200</v>
+        <v>332</v>
       </c>
       <c r="F156" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B157" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -3886,18 +3886,18 @@
         <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="F157" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B158" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F158" t="n">
         <v>49</v>
@@ -3916,10 +3916,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B159" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -3930,18 +3930,18 @@
         <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="F159" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B160" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -3952,18 +3952,18 @@
         <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="F160" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B161" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -3974,18 +3974,18 @@
         <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="F161" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B162" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -3996,18 +3996,18 @@
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="F162" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B163" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -4018,10 +4018,10 @@
         <v>1</v>
       </c>
       <c r="E163" t="n">
-        <v>107</v>
+        <v>524</v>
       </c>
       <c r="F163" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
     </row>
     <row r="164">
@@ -4029,7 +4029,7 @@
         <v>50</v>
       </c>
       <c r="B164" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -4040,15 +4040,15 @@
         <v>1</v>
       </c>
       <c r="E164" t="n">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="F164" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B165" t="n">
         <v>55</v>
@@ -4062,18 +4062,18 @@
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="F165" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B166" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -4084,10 +4084,10 @@
         <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="F166" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/2086.xlsx
+++ b/output/topology_excel/2086.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:J166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
         </is>
       </c>
     </row>
@@ -481,6 +501,10 @@
       <c r="F2" t="n">
         <v>19</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +527,10 @@
       <c r="F3" t="n">
         <v>15</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +553,10 @@
       <c r="F4" t="n">
         <v>16</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +579,10 @@
       <c r="F5" t="n">
         <v>16</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +605,10 @@
       <c r="F6" t="n">
         <v>16</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +631,10 @@
       <c r="F7" t="n">
         <v>17</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +657,10 @@
       <c r="F8" t="n">
         <v>12</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +683,10 @@
       <c r="F9" t="n">
         <v>15</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +709,10 @@
       <c r="F10" t="n">
         <v>15</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +735,10 @@
       <c r="F11" t="n">
         <v>12</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +761,10 @@
       <c r="F12" t="n">
         <v>12</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +787,10 @@
       <c r="F13" t="n">
         <v>12</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +813,10 @@
       <c r="F14" t="n">
         <v>12</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +839,10 @@
       <c r="F15" t="n">
         <v>12</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +865,10 @@
       <c r="F16" t="n">
         <v>12</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +891,10 @@
       <c r="F17" t="n">
         <v>16</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +917,10 @@
       <c r="F18" t="n">
         <v>19</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +943,10 @@
       <c r="F19" t="n">
         <v>19</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +969,10 @@
       <c r="F20" t="n">
         <v>19</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +995,10 @@
       <c r="F21" t="n">
         <v>15</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +1021,10 @@
       <c r="F22" t="n">
         <v>14</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1047,10 @@
       <c r="F23" t="n">
         <v>16</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1073,10 @@
       <c r="F24" t="n">
         <v>16</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1099,10 @@
       <c r="F25" t="n">
         <v>21</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1125,10 @@
       <c r="F26" t="n">
         <v>29</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1151,10 @@
       <c r="F27" t="n">
         <v>23</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1177,10 @@
       <c r="F28" t="n">
         <v>16</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1203,10 @@
       <c r="F29" t="n">
         <v>16</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1229,10 @@
       <c r="F30" t="n">
         <v>9</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1255,10 @@
       <c r="F31" t="n">
         <v>26</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1281,10 @@
       <c r="F32" t="n">
         <v>23</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1307,10 @@
       <c r="F33" t="n">
         <v>16</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1333,10 @@
       <c r="F34" t="n">
         <v>29</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1359,10 @@
       <c r="F35" t="n">
         <v>13</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1385,10 @@
       <c r="F36" t="n">
         <v>13</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1411,10 @@
       <c r="F37" t="n">
         <v>23</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1437,10 @@
       <c r="F38" t="n">
         <v>16</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1463,10 @@
       <c r="F39" t="n">
         <v>13</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1489,10 @@
       <c r="F40" t="n">
         <v>29</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1515,10 @@
       <c r="F41" t="n">
         <v>11</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1541,10 @@
       <c r="F42" t="n">
         <v>17</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1567,10 @@
       <c r="F43" t="n">
         <v>26</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1593,10 @@
       <c r="F44" t="n">
         <v>21</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1619,10 @@
       <c r="F45" t="n">
         <v>26</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1645,10 @@
       <c r="F46" t="n">
         <v>17</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1463,7 +1663,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>131</v>
@@ -1471,6 +1671,10 @@
       <c r="F47" t="n">
         <v>18</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1697,10 @@
       <c r="F48" t="n">
         <v>23</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +1723,10 @@
       <c r="F49" t="n">
         <v>16</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1749,10 @@
       <c r="F50" t="n">
         <v>13</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +1775,10 @@
       <c r="F51" t="n">
         <v>13</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1581,6 +1801,10 @@
       <c r="F52" t="n">
         <v>26</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1603,6 +1827,10 @@
       <c r="F53" t="n">
         <v>21</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +1853,10 @@
       <c r="F54" t="n">
         <v>13</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1647,6 +1879,10 @@
       <c r="F55" t="n">
         <v>21</v>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1661,7 +1897,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
         <v>363</v>
@@ -1669,6 +1905,10 @@
       <c r="F56" t="n">
         <v>87</v>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1691,6 +1931,10 @@
       <c r="F57" t="n">
         <v>16</v>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1713,6 +1957,10 @@
       <c r="F58" t="n">
         <v>29</v>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1733,8 +1981,12 @@
         <v>510</v>
       </c>
       <c r="F59" t="n">
-        <v>55</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1757,6 +2009,10 @@
       <c r="F60" t="n">
         <v>29</v>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1779,6 +2035,10 @@
       <c r="F61" t="n">
         <v>29</v>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1801,6 +2061,10 @@
       <c r="F62" t="n">
         <v>26</v>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1821,8 +2085,12 @@
         <v>469</v>
       </c>
       <c r="F63" t="n">
-        <v>40</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1845,6 +2113,10 @@
       <c r="F64" t="n">
         <v>26</v>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1867,6 +2139,10 @@
       <c r="F65" t="n">
         <v>26</v>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1881,14 +2157,22 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>168</v>
+        <v>29</v>
       </c>
       <c r="F66" t="n">
         <v>26</v>
       </c>
+      <c r="G66" t="n">
+        <v>113</v>
+      </c>
+      <c r="H66" t="n">
+        <v>26</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1909,8 +2193,12 @@
         <v>524</v>
       </c>
       <c r="F67" t="n">
-        <v>40</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1933,6 +2221,10 @@
       <c r="F68" t="n">
         <v>26</v>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1955,6 +2247,10 @@
       <c r="F69" t="n">
         <v>26</v>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1977,6 +2273,10 @@
       <c r="F70" t="n">
         <v>25</v>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1999,6 +2299,10 @@
       <c r="F71" t="n">
         <v>26</v>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2021,6 +2325,10 @@
       <c r="F72" t="n">
         <v>25</v>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2035,14 +2343,22 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>194</v>
+        <v>97</v>
       </c>
       <c r="F73" t="n">
-        <v>109</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G73" t="n">
+        <v>182</v>
+      </c>
+      <c r="H73" t="n">
+        <v>12</v>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2065,6 +2381,10 @@
       <c r="F74" t="n">
         <v>19</v>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2087,6 +2407,10 @@
       <c r="F75" t="n">
         <v>15</v>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2109,6 +2433,10 @@
       <c r="F76" t="n">
         <v>23</v>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2131,6 +2459,10 @@
       <c r="F77" t="n">
         <v>16</v>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2153,6 +2485,10 @@
       <c r="F78" t="n">
         <v>23</v>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2175,6 +2511,10 @@
       <c r="F79" t="n">
         <v>9</v>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2197,6 +2537,10 @@
       <c r="F80" t="n">
         <v>9</v>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2211,13 +2555,25 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="F81" t="n">
-        <v>164</v>
+        <v>13</v>
+      </c>
+      <c r="G81" t="n">
+        <v>74</v>
+      </c>
+      <c r="H81" t="n">
+        <v>13</v>
+      </c>
+      <c r="I81" t="n">
+        <v>151</v>
+      </c>
+      <c r="J81" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="82">
@@ -2241,6 +2597,10 @@
       <c r="F82" t="n">
         <v>13</v>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2263,6 +2623,10 @@
       <c r="F83" t="n">
         <v>13</v>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2285,6 +2649,10 @@
       <c r="F84" t="n">
         <v>21</v>
       </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2307,6 +2675,10 @@
       <c r="F85" t="n">
         <v>13</v>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2329,6 +2701,10 @@
       <c r="F86" t="n">
         <v>16</v>
       </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2351,6 +2727,10 @@
       <c r="F87" t="n">
         <v>23</v>
       </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2373,6 +2753,10 @@
       <c r="F88" t="n">
         <v>29</v>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2395,6 +2779,10 @@
       <c r="F89" t="n">
         <v>16</v>
       </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2417,6 +2805,10 @@
       <c r="F90" t="n">
         <v>16</v>
       </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2439,6 +2831,10 @@
       <c r="F91" t="n">
         <v>29</v>
       </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2453,14 +2849,22 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="F92" t="n">
-        <v>181</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G92" t="n">
+        <v>165</v>
+      </c>
+      <c r="H92" t="n">
+        <v>16</v>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2475,14 +2879,22 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="F93" t="n">
-        <v>98</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G93" t="n">
+        <v>82</v>
+      </c>
+      <c r="H93" t="n">
+        <v>16</v>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2505,6 +2917,10 @@
       <c r="F94" t="n">
         <v>23</v>
       </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2527,6 +2943,10 @@
       <c r="F95" t="n">
         <v>16</v>
       </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2549,6 +2969,10 @@
       <c r="F96" t="n">
         <v>16</v>
       </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2571,6 +2995,10 @@
       <c r="F97" t="n">
         <v>23</v>
       </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2593,6 +3021,10 @@
       <c r="F98" t="n">
         <v>29</v>
       </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2615,6 +3047,10 @@
       <c r="F99" t="n">
         <v>23</v>
       </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2637,6 +3073,10 @@
       <c r="F100" t="n">
         <v>17</v>
       </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2659,6 +3099,10 @@
       <c r="F101" t="n">
         <v>17</v>
       </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2681,6 +3125,10 @@
       <c r="F102" t="n">
         <v>9</v>
       </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2703,6 +3151,10 @@
       <c r="F103" t="n">
         <v>16</v>
       </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2725,6 +3177,10 @@
       <c r="F104" t="n">
         <v>16</v>
       </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2747,6 +3203,10 @@
       <c r="F105" t="n">
         <v>15</v>
       </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2769,6 +3229,10 @@
       <c r="F106" t="n">
         <v>15</v>
       </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2789,8 +3253,12 @@
         <v>75</v>
       </c>
       <c r="F107" t="n">
-        <v>41</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2813,6 +3281,10 @@
       <c r="F108" t="n">
         <v>15</v>
       </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2835,6 +3307,10 @@
       <c r="F109" t="n">
         <v>12</v>
       </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2857,6 +3333,10 @@
       <c r="F110" t="n">
         <v>12</v>
       </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2879,6 +3359,10 @@
       <c r="F111" t="n">
         <v>15</v>
       </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2901,6 +3385,10 @@
       <c r="F112" t="n">
         <v>12</v>
       </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2923,6 +3411,10 @@
       <c r="F113" t="n">
         <v>19</v>
       </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2945,6 +3437,10 @@
       <c r="F114" t="n">
         <v>12</v>
       </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2967,6 +3463,10 @@
       <c r="F115" t="n">
         <v>16</v>
       </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2989,6 +3489,10 @@
       <c r="F116" t="n">
         <v>16</v>
       </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -3011,6 +3515,10 @@
       <c r="F117" t="n">
         <v>17</v>
       </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -3033,6 +3541,10 @@
       <c r="F118" t="n">
         <v>49</v>
       </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -3055,6 +3567,10 @@
       <c r="F119" t="n">
         <v>16</v>
       </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -3077,6 +3593,10 @@
       <c r="F120" t="n">
         <v>16</v>
       </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -3099,6 +3619,10 @@
       <c r="F121" t="n">
         <v>19</v>
       </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -3121,6 +3645,10 @@
       <c r="F122" t="n">
         <v>19</v>
       </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -3143,6 +3671,10 @@
       <c r="F123" t="n">
         <v>15</v>
       </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -3165,6 +3697,10 @@
       <c r="F124" t="n">
         <v>15</v>
       </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -3187,6 +3723,10 @@
       <c r="F125" t="n">
         <v>15</v>
       </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3209,6 +3749,10 @@
       <c r="F126" t="n">
         <v>15</v>
       </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -3231,6 +3775,10 @@
       <c r="F127" t="n">
         <v>15</v>
       </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3253,6 +3801,10 @@
       <c r="F128" t="n">
         <v>17</v>
       </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3275,6 +3827,10 @@
       <c r="F129" t="n">
         <v>17</v>
       </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3297,6 +3853,10 @@
       <c r="F130" t="n">
         <v>41</v>
       </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3319,6 +3879,10 @@
       <c r="F131" t="n">
         <v>21</v>
       </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -3341,6 +3905,10 @@
       <c r="F132" t="n">
         <v>19</v>
       </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -3363,6 +3931,10 @@
       <c r="F133" t="n">
         <v>19</v>
       </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3385,6 +3957,10 @@
       <c r="F134" t="n">
         <v>10</v>
       </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3407,6 +3983,10 @@
       <c r="F135" t="n">
         <v>12</v>
       </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3429,6 +4009,10 @@
       <c r="F136" t="n">
         <v>19</v>
       </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -3451,6 +4035,10 @@
       <c r="F137" t="n">
         <v>12</v>
       </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -3473,6 +4061,10 @@
       <c r="F138" t="n">
         <v>12</v>
       </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -3495,6 +4087,10 @@
       <c r="F139" t="n">
         <v>12</v>
       </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -3517,6 +4113,10 @@
       <c r="F140" t="n">
         <v>12</v>
       </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -3539,6 +4139,10 @@
       <c r="F141" t="n">
         <v>19</v>
       </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -3559,8 +4163,12 @@
         <v>408</v>
       </c>
       <c r="F142" t="n">
-        <v>41</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -3583,6 +4191,10 @@
       <c r="F143" t="n">
         <v>16</v>
       </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -3605,6 +4217,10 @@
       <c r="F144" t="n">
         <v>19</v>
       </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -3627,6 +4243,10 @@
       <c r="F145" t="n">
         <v>19</v>
       </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -3649,6 +4269,10 @@
       <c r="F146" t="n">
         <v>19</v>
       </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -3671,6 +4295,10 @@
       <c r="F147" t="n">
         <v>19</v>
       </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -3693,6 +4321,10 @@
       <c r="F148" t="n">
         <v>19</v>
       </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -3715,6 +4347,10 @@
       <c r="F149" t="n">
         <v>19</v>
       </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -3737,6 +4373,10 @@
       <c r="F150" t="n">
         <v>15</v>
       </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -3759,6 +4399,10 @@
       <c r="F151" t="n">
         <v>14</v>
       </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -3781,6 +4425,10 @@
       <c r="F152" t="n">
         <v>23</v>
       </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -3803,6 +4451,10 @@
       <c r="F153" t="n">
         <v>23</v>
       </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -3825,6 +4477,10 @@
       <c r="F154" t="n">
         <v>26</v>
       </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -3839,14 +4495,22 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E155" t="n">
-        <v>252</v>
+        <v>213</v>
       </c>
       <c r="F155" t="n">
-        <v>226</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G155" t="n">
+        <v>239</v>
+      </c>
+      <c r="H155" t="n">
+        <v>13</v>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -3869,6 +4533,10 @@
       <c r="F156" t="n">
         <v>13</v>
       </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -3891,6 +4559,10 @@
       <c r="F157" t="n">
         <v>21</v>
       </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -3911,8 +4583,12 @@
         <v>77</v>
       </c>
       <c r="F158" t="n">
-        <v>49</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -3935,6 +4611,10 @@
       <c r="F159" t="n">
         <v>11</v>
       </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -3957,6 +4637,10 @@
       <c r="F160" t="n">
         <v>17</v>
       </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -3979,6 +4663,10 @@
       <c r="F161" t="n">
         <v>26</v>
       </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -4001,6 +4689,10 @@
       <c r="F162" t="n">
         <v>29</v>
       </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -4021,8 +4713,12 @@
         <v>524</v>
       </c>
       <c r="F163" t="n">
-        <v>55</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -4045,6 +4741,10 @@
       <c r="F164" t="n">
         <v>21</v>
       </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -4067,6 +4767,10 @@
       <c r="F165" t="n">
         <v>21</v>
       </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -4089,6 +4793,10 @@
       <c r="F166" t="n">
         <v>13</v>
       </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
